--- a/healthcare_forms/028_mpox_engagement_fund_form--healthcare_forms.xlsx
+++ b/healthcare_forms/028_mpox_engagement_fund_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'local_health_department',_'label':_'local_health_department'}</t>
+          <t>local_health_department</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Local Health Department', 'label': 'Local Health Department'}</t>
+          <t>Local Health Department</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'state_health_department',_'label':_'state_health_department'}</t>
+          <t>state_health_department</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'State Health Department', 'label': 'State Health Department'}</t>
+          <t>State Health Department</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'vaccination',_'label':_'vaccination'}</t>
+          <t>vaccination</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Vaccination', 'label': 'Vaccination'}</t>
+          <t>Vaccination</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'testing',_'label':_'testing'}</t>
+          <t>testing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Testing', 'label': 'Testing'}</t>
+          <t>Testing</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'education',_'label':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Education', 'label': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'contact_tracing',_'label':_'contact_tracing'}</t>
+          <t>contact_tracing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Contact Tracing', 'label': 'Contact Tracing'}</t>
+          <t>Contact Tracing</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
